--- a/Modules/WF/WF_BOM.xlsx
+++ b/Modules/WF/WF_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\WF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E555D1-AA09-4270-97F1-3CCFD2ABB7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E897BB28-4749-4F5B-A476-8E5D7523FB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -251,13 +251,7 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
-  </si>
-  <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
   </si>
   <si>
     <t>Jack Nut</t>
@@ -555,6 +549,12 @@
       </rPr>
       <t>***</t>
     </r>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1464,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1499,7 +1499,7 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
@@ -1508,7 +1508,7 @@
         <v>48</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>57</v>
@@ -1522,7 +1522,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -1531,7 +1531,7 @@
         <v>48</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>57</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
         <v>35</v>
@@ -1557,7 +1557,7 @@
         <v>57</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -1580,7 +1580,7 @@
         <v>57</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1591,7 +1591,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -1600,7 +1600,7 @@
         <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>57</v>
@@ -1614,7 +1614,7 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
         <v>34</v>
@@ -1623,7 +1623,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>57</v>
@@ -1637,7 +1637,7 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
         <v>30</v>
@@ -1646,7 +1646,7 @@
         <v>48</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>57</v>
@@ -1660,7 +1660,7 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
         <v>36</v>
@@ -1672,7 +1672,7 @@
         <v>57</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1683,7 +1683,7 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
         <v>29</v>
@@ -1695,7 +1695,7 @@
         <v>57</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1715,10 +1715,10 @@
         <v>49</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1729,19 +1729,19 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1752,19 +1752,19 @@
         <v>6</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1775,19 +1775,19 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1798,19 +1798,19 @@
         <v>5</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
         <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1830,10 +1830,10 @@
         <v>45</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1853,10 +1853,10 @@
         <v>43</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1876,10 +1876,10 @@
         <v>44</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1899,7 +1899,7 @@
         <v>51</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>58</v>
@@ -1922,10 +1922,10 @@
         <v>46</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1939,10 +1939,10 @@
         <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>59</v>
@@ -1953,13 +1953,13 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
         <v>42</v>
@@ -1968,7 +1968,7 @@
         <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1982,16 +1982,16 @@
         <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
         <v>41</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2005,16 +2005,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E25" t="s">
         <v>41</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2034,10 +2034,10 @@
         <v>41</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2051,13 +2051,13 @@
         <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="J28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -2065,19 +2065,19 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
         <v>71</v>
       </c>
       <c r="E29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="J29" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2097,27 +2097,27 @@
         <v>70</v>
       </c>
       <c r="J30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2136,22 +2136,22 @@
     <hyperlink ref="F22" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
     <hyperlink ref="F23" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="F30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="F28" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="F29" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F24:F26" r:id="rId17" display="https://www.tme.eu/hr/en/details/zl211-40kg-s/pin-headers/connfly/ds1022-1-40ruf11/" xr:uid="{564A2D52-8874-460F-A304-E4F89861A78E}"/>
-    <hyperlink ref="F24" r:id="rId18" xr:uid="{2C4CAA6B-8E09-4535-952E-F17E97348B39}"/>
-    <hyperlink ref="F25" r:id="rId19" xr:uid="{888EC6AF-9993-451F-BA80-D55DBB11E481}"/>
-    <hyperlink ref="F26" r:id="rId20" xr:uid="{6FB4E357-A487-4449-A1B3-F4548852D8DB}"/>
-    <hyperlink ref="F3" r:id="rId21" xr:uid="{8901D116-9012-4D3A-ABF7-D179B26B85D1}"/>
-    <hyperlink ref="F4" r:id="rId22" xr:uid="{D586E3B9-035C-45F6-AC6D-C881FAED7847}"/>
-    <hyperlink ref="J5" r:id="rId23" xr:uid="{451E279F-07F2-4DEF-8ED1-12122DA2BF0B}"/>
-    <hyperlink ref="J6" r:id="rId24" xr:uid="{CDFCF192-71FB-420C-9F00-BC64F79EF165}"/>
-    <hyperlink ref="F7" r:id="rId25" xr:uid="{0E32C874-E18F-4C11-857E-7848A894E788}"/>
-    <hyperlink ref="F8" r:id="rId26" xr:uid="{B72391F5-B8C8-4CA2-9902-5F31C9021A49}"/>
-    <hyperlink ref="F9" r:id="rId27" xr:uid="{5456E219-423C-47B1-BE36-20268F0D9FB1}"/>
-    <hyperlink ref="J10" r:id="rId28" xr:uid="{8AA85E49-D000-42A4-9DEC-A6CC11A0CAD6}"/>
-    <hyperlink ref="J11" r:id="rId29" xr:uid="{81998E97-214A-44BC-B336-C12010548454}"/>
-    <hyperlink ref="F20" r:id="rId30" xr:uid="{1562FF91-358C-45DE-8371-E2F58F9E41C7}"/>
+    <hyperlink ref="F24:F26" r:id="rId15" display="https://www.tme.eu/hr/en/details/zl211-40kg-s/pin-headers/connfly/ds1022-1-40ruf11/" xr:uid="{564A2D52-8874-460F-A304-E4F89861A78E}"/>
+    <hyperlink ref="F24" r:id="rId16" xr:uid="{2C4CAA6B-8E09-4535-952E-F17E97348B39}"/>
+    <hyperlink ref="F25" r:id="rId17" xr:uid="{888EC6AF-9993-451F-BA80-D55DBB11E481}"/>
+    <hyperlink ref="F26" r:id="rId18" xr:uid="{6FB4E357-A487-4449-A1B3-F4548852D8DB}"/>
+    <hyperlink ref="F3" r:id="rId19" xr:uid="{8901D116-9012-4D3A-ABF7-D179B26B85D1}"/>
+    <hyperlink ref="F4" r:id="rId20" xr:uid="{D586E3B9-035C-45F6-AC6D-C881FAED7847}"/>
+    <hyperlink ref="J5" r:id="rId21" xr:uid="{451E279F-07F2-4DEF-8ED1-12122DA2BF0B}"/>
+    <hyperlink ref="J6" r:id="rId22" xr:uid="{CDFCF192-71FB-420C-9F00-BC64F79EF165}"/>
+    <hyperlink ref="F7" r:id="rId23" xr:uid="{0E32C874-E18F-4C11-857E-7848A894E788}"/>
+    <hyperlink ref="F8" r:id="rId24" xr:uid="{B72391F5-B8C8-4CA2-9902-5F31C9021A49}"/>
+    <hyperlink ref="F9" r:id="rId25" xr:uid="{5456E219-423C-47B1-BE36-20268F0D9FB1}"/>
+    <hyperlink ref="J10" r:id="rId26" xr:uid="{8AA85E49-D000-42A4-9DEC-A6CC11A0CAD6}"/>
+    <hyperlink ref="J11" r:id="rId27" xr:uid="{81998E97-214A-44BC-B336-C12010548454}"/>
+    <hyperlink ref="F20" r:id="rId28" xr:uid="{1562FF91-358C-45DE-8371-E2F58F9E41C7}"/>
+    <hyperlink ref="F28" r:id="rId29" xr:uid="{850073B2-78AE-4709-AF45-3E4CB51AE3DD}"/>
+    <hyperlink ref="F29" r:id="rId30" xr:uid="{531E1C17-90DF-4F57-9297-3FE8668D9F21}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
